--- a/data/kz/17_permits.xlsx
+++ b/data/kz/17_permits.xlsx
@@ -519,6 +519,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1137,7 +1138,6 @@
           <t>10-30 МРП</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PHARMACY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
